--- a/docs/ValueSet-RoupasUsadasMedicao.xlsx
+++ b/docs/ValueSet-RoupasUsadasMedicao.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -108,19 +108,19 @@
     <t>LA11871-3</t>
   </si>
   <si>
-    <t>Roupa íntima ou menos</t>
+    <t>Underwear or less</t>
   </si>
   <si>
     <t>LA11872-1</t>
   </si>
   <si>
-    <t>Roupas de rua, sem sapatos</t>
+    <t>Street clothes, no shoes</t>
   </si>
   <si>
     <t>LA11873-9</t>
   </si>
   <si>
-    <t>Roupas e sapatos de rua</t>
+    <t>Street clothes &amp; shoes</t>
   </si>
   <si>
     <t/>
